--- a/artfynd/A 63596-2021 artfynd.xlsx
+++ b/artfynd/A 63596-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131039026</v>
       </c>
       <c r="B2" t="n">
-        <v>97291</v>
+        <v>97294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 63596-2021 artfynd.xlsx
+++ b/artfynd/A 63596-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131039026</v>
       </c>
       <c r="B2" t="n">
-        <v>97294</v>
+        <v>97295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 63596-2021 artfynd.xlsx
+++ b/artfynd/A 63596-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131039026</v>
       </c>
       <c r="B2" t="n">
-        <v>97295</v>
+        <v>97297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 63596-2021 artfynd.xlsx
+++ b/artfynd/A 63596-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131039026</v>
       </c>
       <c r="B2" t="n">
-        <v>97297</v>
+        <v>97298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 63596-2021 artfynd.xlsx
+++ b/artfynd/A 63596-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131039026</v>
+        <v>131039027</v>
       </c>
       <c r="B2" t="n">
-        <v>97298</v>
+        <v>97367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stubbtrådmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscocephaloziopsis catenulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338319</v>
+        <v>338330</v>
       </c>
       <c r="R2" t="n">
-        <v>6391894</v>
+        <v>6391902</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -770,6 +769,405 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131039029</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96601</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björröd, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>338317</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6391932</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Landvetter</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>90772379</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97394</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Härryda kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>338329</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6391889</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Landvetter</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-11-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-11-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>måttlig förekomst på granlåga</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>JSN0127 Härryda naturvårdsplan 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131039026</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97394</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björröd, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>338319</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6391894</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Landvetter</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131039028</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97394</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björröd, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>338321</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6391932</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Landvetter</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63596-2021 artfynd.xlsx
+++ b/artfynd/A 63596-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039027</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039029</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
           <t>JSN0127 Härryda naturvårdsplan 2020</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90772379</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,8 +1193,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131039028</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>